--- a/stories/arbres/ATOM-FAM.SEC.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est bientôt l'anniversaire de papa. Jules est dans la cuisine avec maman. Ils font un gâteau au citron. La pâte est jaune. Ça sent bon. Maman dit : c'est une surprise gentille. On la garde un peu. Jules sourit. Il range le moule. Ses mains sont un peu collantes. Papa entre. Papa dit : ça sent bon ici. Jules a envie de dire. Maman chuchote : encore un tout petit peu. Le soir, la table est prête. Le gâteau est là. Les bougies sont petites. Jules dit : papa, surprise. C'est pour toi. Papa ouvre les yeux grands. Papa dit : merci Jules. Maman dit : une surprise gentille, on la garde un peu, puis on dit.</t>
+          <t>C'est bientôt l'anniversaire de papa. Jules est dans la cuisine avec maman. Ils font un gâteau au citron. La pâte est jaune. Ça sent bon. C'est une surprise gentille. On la garde un peu. Jules sourit. Il range le moule. Ses mains sont un peu collantes. Papa entre. Ça sent bon ici. Jules a envie de dire. Maman chuchote : encore un tout petit peu. Le soir, la table est prête. Le gâteau est là. Les bougies sont petites. Papa, surprise. C'est pour toi. Papa ouvre les yeux grands. Merci Jules. Une surprise gentille, on la garde un peu, puis on dit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est bientôt l'anniversaire de papa. Jules est dans la cuisine avec maman. Ils font un gâteau au citron. La pâte est jaune. Ça sent bon.
+maman|C'est une surprise gentille. On la garde un peu.
+narrateur|Jules sourit. Il range le moule. Ses mains sont un peu collantes. Papa entre.
+papa|Ça sent bon ici.
+narrateur|Jules a envie de dire. Maman chuchote : encore un tout petit peu. Le soir, la table est prête. Le gâteau est là. Les bougies sont petites.
+enfant-m|Papa, surprise. C'est pour toi. Papa ouvre les yeux grands.
+papa|Merci Jules.
+maman|Une surprise gentille, on la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le gâteau pour papa, c'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a gardé un peu. Puis il a dit. Papa a vu le gâteau. C'était une surprise gentille, courte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa goûte une part. Jules goûte aussi. C'est acide et doux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 maman|Une surprise gentille, on la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Le gâteau pour papa, c'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Jules a gardé un peu. Puis il a dit. Papa a vu le gâteau. C'était une surprise gentille, courte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Papa goûte une part. Jules goûte aussi. C'est acide et doux.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La surprise gentille de Jules</t>
+          <t>Le gâteau au citron d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir et maman font un gâteau au citron. Ils gardent un peu. Le soir, ils disent. Papa découvre la surprise gentille.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est bientôt l'anniversaire de papa. Jules est dans la cuisine avec maman. Ils font un gâteau au citron. La pâte est jaune. Ça sent bon. C'est une surprise gentille. On la garde un peu. Jules sourit. Il range le moule. Ses mains sont un peu collantes. Papa entre. Ça sent bon ici. Jules a envie de dire. Maman chuchote : encore un tout petit peu. Le soir, la table est prête. Le gâteau est là. Les bougies sont petites. Papa, surprise. C'est pour toi. Papa ouvre les yeux grands. Merci Jules. Une surprise gentille, on la garde un peu, puis on dit.</t>
+          <t>Sur la table, la farine fait une petite neige. Un citron jaune brille dans le saladier. La cuisine sent le fruit et le bois. Dehors, le vent pousse une feuille. La feuille tape la vitre, tout doux. Papa est encore un peu loin. Maman essuie le bord du saladier. Amir, tu veux un tablier ? Oui, le bleu. Le tablier est un peu grand. Les poches sentent la farine. Bientôt, c'est l'anniversaire de papa. On fait un gâteau au citron. Il aime le citron. Oui, beaucoup. En ce moment, Amir casse un œuf. Le jaune tombe, tout rond. On mélange, tout doux. La cuillère fait un petit bruit. La pâte devient jaune, lisse. Ça sent le citron, fort et bon. Mes mains sont collantes. On se les essuie. C'est une surprise gentille. On la garde un peu. On la garde un peu. Amir verse la pâte dans le moule. Le moule est rond, un peu lourd. On attend, tout calme. Plus tard, le gâteau est prêt. Amir range le moule près du mur. La porte s'ouvre. Papa entre, les chaussures un peu mouillées. Ça sent bon ici. Je peux le dire ? Encore un tout petit peu. Amir serre les lèvres. Il garde encore un peu. Je vais laver mes mains. Le soir, la table est prête. Une nappe blanche, des petites assiettes. Le gâteau est là, jaune et haut. Les bougies sont toutes petites. Maintenant, on dit. Papa, surprise. C'est pour toi. Papa ouvre les yeux, tout grands. Un gâteau au citron. Merci, Amir. Une surprise gentille, on la garde un peu. Puis on dit. Puis on dit. Bravo, Amir. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est bientôt l'anniversaire de papa. Jules est dans la cuisine avec maman. Ils font un gâteau au citron. La pâte est jaune. Ça sent bon.
-maman|C'est une surprise gentille. On la garde un peu.
-narrateur|Jules sourit. Il range le moule. Ses mains sont un peu collantes. Papa entre.
+          <t>narrateur|Sur la table, la farine fait une petite neige.
+narrateur|Un citron jaune brille dans le saladier.
+narrateur|La cuisine sent le fruit et le bois.
+narrateur|Dehors, le vent pousse une feuille.
+narrateur|La feuille tape la vitre, tout doux.
+narrateur|Papa est encore un peu loin.
+narrateur|Maman essuie le bord du saladier.
+maman|Amir, tu veux un tablier ?
+enfant-m|Oui, le bleu.
+narrateur|Le tablier est un peu grand.
+narrateur|Les poches sentent la farine.
+maman|Bientôt, c'est l'anniversaire de papa.
+maman|On fait un gâteau au citron.
+enfant-m|Il aime le citron.
+maman|Oui, beaucoup.
+narrateur|En ce moment, Amir casse un œuf.
+narrateur|Le jaune tombe, tout rond.
+maman|On mélange, tout doux.
+narrateur|La cuillère fait un petit bruit.
+narrateur|La pâte devient jaune, lisse.
+narrateur|Ça sent le citron, fort et bon.
+enfant-m|Mes mains sont collantes.
+maman|On se les essuie.
+maman|C'est une surprise gentille.
+maman|On la garde un peu.
+enfant-m|On la garde un peu.
+narrateur|Amir verse la pâte dans le moule.
+narrateur|Le moule est rond, un peu lourd.
+maman|On attend, tout calme.
+narrateur|Plus tard, le gâteau est prêt.
+narrateur|Amir range le moule près du mur.
+narrateur|La porte s'ouvre.
+narrateur|Papa entre, les chaussures un peu mouillées.
 papa|Ça sent bon ici.
-narrateur|Jules a envie de dire. Maman chuchote : encore un tout petit peu. Le soir, la table est prête. Le gâteau est là. Les bougies sont petites.
-enfant-m|Papa, surprise. C'est pour toi. Papa ouvre les yeux grands.
-papa|Merci Jules.
-maman|Une surprise gentille, on la garde un peu, puis on dit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-m|Je peux le dire ?
+maman|Encore un tout petit peu.
+narrateur|Amir serre les lèvres.
+narrateur|Il garde encore un peu.
+papa|Je vais laver mes mains.
+narrateur|Le soir, la table est prête.
+narrateur|Une nappe blanche, des petites assiettes.
+narrateur|Le gâteau est là, jaune et haut.
+narrateur|Les bougies sont toutes petites.
+maman|Maintenant, on dit.
+enfant-m|Papa, surprise.
+enfant-m|C'est pour toi.
+narrateur|Papa ouvre les yeux, tout grands.
+papa|Un gâteau au citron.
+papa|Merci, Amir.
+maman|Une surprise gentille, on la garde un peu.
+maman|Puis on dit.
+enfant-m|Puis on dit.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cuisine</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1531,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules a gardé un peu. Puis il a dit. Papa a vu le gâteau. C'était une surprise gentille, courte.</t>
+          <t>Amir a gardé un peu. Puis il a dit. Papa a vu le gâteau. C'était une surprise gentille, courte. Tu as gardé un peu. Puis tu as dit. Surprise gentille. Puis on dit. Bravo, Amir. Une bougie fait une petite lumière. Je souffle, tout doux. Joyeux anniversaire, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,7 +1737,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules a gardé un peu. Puis il a dit. Papa a vu le gâteau. C'était une surprise gentille, courte.</t>
+          <t>narrateur|Amir a gardé un peu.
+narrateur|Puis il a dit.
+narrateur|Papa a vu le gâteau.
+maman|C'était une surprise gentille, courte.
+papa|Tu as gardé un peu.
+papa|Puis tu as dit.
+enfant-m|Surprise gentille.
+enfant-m|Puis on dit.
+maman|Bravo, Amir.
+narrateur|Une bougie fait une petite lumière.
+papa|Je souffle, tout doux.
+enfant-m|Joyeux anniversaire, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa goûte une part. Jules goûte aussi. C'est acide et doux.</t>
+          <t>Papa goûte une part. Amir goûte aussi. C'est acide, et un peu doux. Le citron pique un tout petit peu. J'aime bien. Tes mains sont propres, maintenant. Une miette reste sur la nappe. La petite neige de farine n'est plus là. Merci pour la surprise. On l'a gardée un peu. Puis on a dit. C'est ça. Dehors, le vent est calme. On range les assiettes ensemble. Moi, je porte la petite. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,7 +1912,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa goûte une part. Jules goûte aussi. C'est acide et doux.</t>
+          <t>narrateur|Papa goûte une part.
+narrateur|Amir goûte aussi.
+narrateur|C'est acide, et un peu doux.
+papa|Le citron pique un tout petit peu.
+enfant-m|J'aime bien.
+maman|Tes mains sont propres, maintenant.
+narrateur|Une miette reste sur la nappe.
+narrateur|La petite neige de farine n'est plus là.
+papa|Merci pour la surprise.
+enfant-m|On l'a gardée un peu.
+maman|Puis on a dit.
+papa|C'est ça.
+narrateur|Dehors, le vent est calme.
+maman|On range les assiettes ensemble.
+enfant-m|Moi, je porte la petite.
+papa|Bravo.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1867,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Amir. Le gâteau était bon. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2095,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a gardé un peu.
+enfant-m|Puis on a dit.
+maman|Bravo, Amir.
+papa|Le gâteau était bon.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2159,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sur la table, la farine fait une petite neige. Un citron jaune brille dans le saladier. La cuisine sent le fruit et le bois. Dehors, le vent pousse une feuille. La feuille tape la vitre, tout doux. Papa est encore un peu loin. Maman essuie le bord du saladier. Amir, tu veux un tablier ? Oui, le bleu. Le tablier est un peu grand. Les poches sentent la farine. Bientôt, c'est l'anniversaire de papa. On fait un gâteau au citron. Il aime le citron. Oui, beaucoup. En ce moment, Amir casse un œuf. Le jaune tombe, tout rond. On mélange, tout doux. La cuillère fait un petit bruit. La pâte devient jaune, lisse. Ça sent le citron, fort et bon. Mes mains sont collantes. On se les essuie. C'est une surprise gentille. On la garde un peu. On la garde un peu. Amir verse la pâte dans le moule. Le moule est rond, un peu lourd. On attend, tout calme. Plus tard, le gâteau est prêt. Amir range le moule près du mur. La porte s'ouvre. Papa entre, les chaussures un peu mouillées. Ça sent bon ici. Je peux le dire ? Encore un tout petit peu. Amir serre les lèvres. Il garde encore un peu. Je vais laver mes mains. Le soir, la table est prête. Une nappe blanche, des petites assiettes. Le gâteau est là, jaune et haut. Les bougies sont toutes petites. Maintenant, on dit. Papa, surprise. C'est pour toi. Papa ouvre les yeux, tout grands. Un gâteau au citron. Merci, Amir. Une surprise gentille, on la garde un peu. Puis on dit. Puis on dit. Bravo, Amir. Tu as fait du bon travail.</t>
+          <t>Sur la table, la farine fait une petite neige. Un citron jaune brille dans le saladier. La cuisine sent le fruit et le bois. Dehors, le vent pousse une feuille. La feuille tape la vitre, tout doux. Papa est encore un peu loin. Maman essuie le bord du saladier. Amir, tu veux un tablier ? Oui, le bleu. Le tablier est un peu grand. Les poches sentent la farine. Bientôt, c'est l'anniversaire de papa. On fait un gâteau au citron. Il aime le citron. Oui, beaucoup. En ce moment, Amir casse un œuf. Le jaune tombe, tout rond. On mélange, tout doux. La cuillère fait un petit bruit. La pâte devient jaune, lisse. Ça sent le citron, fort et bon. Mes mains sont collantes. On se les essuie. C'est une surprise gentille. On la garde un peu. On la garde un peu. Amir verse la pâte dans le moule. Le moule est rond, un peu lourd. On attend, tout calme. Plus tard, le gâteau est prêt. Amir range le moule près du mur. La porte s'ouvre. Papa entre, les chaussures un peu mouillées. Ça sent bon ici. Je peux le dire ? Encore un tout petit peu. Amir serre les lèvres. Il garde encore un peu. Je vais laver mes mains. Le soir, la table est prête. Une nappe blanche, des petites assiettes. Le gâteau est là, jaune et haut. Les bougies sont toutes petites. Maintenant, on dit. Papa, surprise. C'est pour toi. Papa ouvre les yeux, tout grands. Un gâteau au citron. Merci, Amir. Une surprise gentille, on la garde un peu. Puis on dit. Puis on dit. Bravo, Amir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;C'est bientôt l'anniversaire de papa. Jules est dans la cuisine avec maman. Ils font un gâteau au citron. La pâte est jaune. Ça sent bon. Maman dit : c'est une &lt;emphasis level="moderate"&gt;surprise&lt;/emphasis&gt; gentille. On la garde un peu. Jules sourit. Il range le moule. Ses mains sont un peu collantes. Papa entre. Papa dit : ça sent bon ici. Jules a envie de dire. Maman chuchote : encore un tout petit peu. Le soir, la table est prête. Le gâteau est là. Les bougies sont petites. Jules dit : papa, surprise. C'est pour toi. Papa ouvre les yeux grands. Papa dit : merci Jules. Maman dit : une surprise gentille, on la garde un peu, puis on dit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur la table, la farine fait une petite neige. Un citron jaune brille dans le saladier. La cuisine sent le fruit et le bois. Dehors, le vent pousse une feuille. La feuille tape la vitre, tout doux. Papa est encore un peu loin. Maman essuie le bord du saladier. Amir, tu veux un tablier ? Oui, le bleu. Le tablier est un peu grand. Les poches sentent la farine. Bientôt, c'est l'anniversaire de papa. On fait un gâteau au citron. Il aime le citron. Oui, beaucoup. En ce moment, Amir casse un œuf. Le jaune tombe, tout rond. On mélange, tout doux. La cuillère fait un petit bruit. La pâte devient jaune, lisse. Ça sent le citron, fort et bon. Mes mains sont collantes. On se les essuie. C'est une surprise gentille. On la garde un peu. On la garde un peu. Amir verse la pâte dans le moule. Le moule est rond, un peu lourd. On attend, tout calme. Plus tard, le gâteau est prêt. Amir range le moule près du mur. La porte s'ouvre. Papa entre, les chaussures un peu mouillées. Ça sent bon ici. Je peux le dire ? Encore un tout petit peu. Amir serre les lèvres. Il garde encore un peu. Je vais laver mes mains. Le soir, la table est prête. Une nappe blanche, des petites assiettes. Le gâteau est là, jaune et haut. Les bougies sont toutes petites. Maintenant, on dit. Papa, surprise. C'est pour toi. Papa ouvre les yeux, tout grands. Un gâteau au citron. Merci, Amir. Une surprise gentille, on la garde un peu. Puis on dit. Puis on dit. Bravo, Amir.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1376,8 +1376,7 @@
 maman|Une surprise gentille, on la garde un peu.
 maman|Puis on dit.
 enfant-m|Puis on dit.
-papa|Bravo, Amir.
-papa|Tu as fait du bon travail.</t>
+papa|Bravo, Amir.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1414,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le gâteau pour papa, c'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le gâteau pour papa, c'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1568,7 +1567,6 @@
           <t>narrateur|Le gâteau pour papa, c'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1598,7 +1596,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules a gardé un peu. Puis il a dit. Papa a vu le gâteau. C'était une &lt;emphasis level="moderate"&gt;surprise&lt;/emphasis&gt; gentille, courte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a gardé un peu. Puis il a dit. Papa a vu le gâteau. C'était une surprise gentille, courte. Tu as gardé un peu. Puis tu as dit. Surprise gentille. Puis on dit. Bravo, Amir. Une bougie fait une petite lumière. Je souffle, tout doux. Joyeux anniversaire, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1751,7 +1749,6 @@
 enfant-m|Joyeux anniversaire, papa.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1781,7 +1778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa goûte une part. Jules goûte aussi. C'est acide et doux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa goûte une part. Amir goûte aussi. C'est acide, et un peu doux. Le citron pique un tout petit peu. J'aime bien. Tes mains sont propres, maintenant. Une miette reste sur la nappe. La petite neige de farine n'est plus là. Merci pour la surprise. On l'a gardée un peu. Puis on a dit. C'est ça. Dehors, le vent est calme. On range les assiettes ensemble. Moi, je porte la petite. Bravo.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1930,7 +1927,6 @@
 papa|Bravo.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1955,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a gardé un peu. Puis on a dit. Bravo, Amir. Le gâteau était bon. L'histoire est finie.</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Amir. Le gâteau était bon.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Amir. Le gâteau était bon.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,11 +2094,9 @@
           <t>enfant-m|On a gardé un peu.
 enfant-m|Puis on a dit.
 maman|Bravo, Amir.
-papa|Le gâteau était bon.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Le gâteau était bon.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2121,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2166,6 +2160,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jules, maman, papa</t>
+          <t>Amir, papa, maman</t>
         </is>
       </c>
     </row>
